--- a/mockdata/single_file/Single_File_Upload.xlsx
+++ b/mockdata/single_file/Single_File_Upload.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC8"/>
+  <dimension ref="A1:AD8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -439,125 +439,130 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>River Name</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Isolation source</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Collection Date</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Latitude</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Longitude</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Collected By</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>AMR Resistance genes</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Sequence Name</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Element type</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Class</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Subclass</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Target length</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Reference sequence length</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>% Coverage of reference sequence</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>% Identity to reference sequence</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Alignment Length</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Accession of Closest Sequence</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Virulence Genes</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Plasmid Replicons</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Predicted SIR profile</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>pH</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Temp of water</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>TDS (mg/L)</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>Dissolved Oxygen (mg/L)</t>
         </is>
@@ -586,125 +591,130 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>Paarl</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>Berg River</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>River Water</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>12-03-2025</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>-33.7342</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>18.9621</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>jane.doe@tuks.co.za</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>blaCTX-M-15</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>CTX-M family extended-spectrum class A beta-lactamase</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>AMR</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>BETA-LACTAM</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>CEPHALOSPORIN</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>876</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>876</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>99,10</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>98,50</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>868</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>WP_000089570.1</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>eaeA</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>IncFIB(K)</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>7,2</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>18,3</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>145</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>6,1</t>
         </is>
@@ -733,125 +743,130 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>Paarl</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>Berg River</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>River Water</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>12-03-2025</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>-33.7342</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>18.9621</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>jane.doe@tuks.co.za</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>tet(A)</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>tetracycline efflux MFS transporter Tet(A)</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>AMR</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>TETRACYCLINE</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>TETRACYCLINE</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>1200</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>1200</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>96,20</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>94,70</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>1140</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>WP_000841444.1</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>eaeA</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>IncFIB(K)</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>7,2</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>18,3</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>145</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>6,1</t>
         </is>
@@ -880,125 +895,130 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>Paarl</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>Berg River</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>River sediment</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>12-03-2025</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>-33.7342</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>18.9621</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>jane.doe@tuks.co.za</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>sul1</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>sulfonamide-resistant dihydropteroate synthase Sul1</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>AMR</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>SULFONAMIDE</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>SULFONAMIDE</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>840</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>840</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>95,50</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>97,00</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>820</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>WP_000259031.1</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>invA</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>IncHI2</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>7,2</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>18,3</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>145</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>6,1</t>
         </is>
@@ -1027,125 +1047,130 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t>Wellington</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>Berg River</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>Agricultural runoff</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>13-03-2025</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>-33.6400</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>19.0112</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>john.smith@tuks.co.za</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>blaKPC-2</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>KPC family carbapenem-hydrolyzing class A beta-lactamase</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>AMR</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>BETA-LACTAM</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>CARBAPENEM</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>882</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>882</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>100,00</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>99,80</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>882</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>WP_004199234.1</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>fyuA</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>IncFII(K)</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>6,9</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>19,1</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>162</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>5,4</t>
         </is>
@@ -1174,125 +1199,130 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t>Wellington</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>Berg River</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>Agricultural runoff</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>13-03-2025</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>-33.6400</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>19.0112</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>john.smith@tuks.co.za</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>aac(6')-Ib</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>aminoglycoside N-acetyltransferase AAC(6')-Ib</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>AMR</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>AMINOGLYCOSIDE</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>AMIKACIN</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>600</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>600</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>94,00</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>92,30</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>565</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>WP_032493347.1</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>fyuA</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>IncFII(K)</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>6,9</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>19,1</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>162</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>5,4</t>
         </is>
@@ -1321,117 +1351,122 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t>Franschhoek</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>Berg River</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>River Water</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>14-03-2025</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>-33.9118</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>19.1206</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>jane.doe@tuks.co.za</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>vanA</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>D-alanine--D-lactate ligase VanA</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>AMR</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>GLYCOPEPTIDE</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>VANCOMYCIN</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>1032</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>1032</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>98,00</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>96,40</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>1010</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>WP_002413262.1</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="inlineStr">
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>7,5</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>17,8</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>138</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>6,7</t>
         </is>
@@ -1460,121 +1495,126 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t>Franschhoek</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>Berg River</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>River sediment</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>14-03-2025</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>-33.9118</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>19.1206</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>jane.doe@tuks.co.za</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>blaOXA-23</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>OXA-23 family carbapenem-hydrolyzing class D beta-lactamase</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>AMR</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>BETA-LACTAM</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>CARBAPENEM</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>822</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>822</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>99,60</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>99,10</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>820</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>WP_000724420.1</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr"/>
-      <c r="X8" t="inlineStr">
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr">
         <is>
           <t>IncL/M</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>7,5</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>17,8</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>138</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>6,7</t>
         </is>
